--- a/InputData/elec/BZECfNP/BAU Zero Emis Credit for Nuc Plants.xlsx
+++ b/InputData/elec/BZECfNP/BAU Zero Emis Credit for Nuc Plants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\elec\BZECfNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA17051-7C54-4F0B-8BB0-ACC624F592F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DB0CD19-45FE-44D4-B4CE-FAC067FEFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" activeTab="1" xr2:uid="{C5EFE8E4-8660-49B5-88C2-8D099D44E411}"/>
+    <workbookView xWindow="720" yWindow="660" windowWidth="16755" windowHeight="14505" activeTab="1" xr2:uid="{C5EFE8E4-8660-49B5-88C2-8D099D44E411}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -847,9 +847,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD24FED-1FE2-4888-B6B4-6A2AD33A9CF5}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,7 +857,7 @@
         <v>103</v>
       </c>
       <c r="C1" s="8">
-        <v>45237</v>
+        <v>45293</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>38</v>
@@ -866,7 +866,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="str">
         <f>LOOKUP(B1,F1:G50,G1:G50)</f>
         <v>ND</v>
@@ -878,7 +878,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -892,7 +892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4">
         <v>2019</v>
       </c>
@@ -903,7 +903,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -914,7 +914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
@@ -925,7 +925,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F7" s="7" t="s">
         <v>50</v>
       </c>
@@ -933,7 +933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -944,7 +944,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -955,7 +955,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -966,7 +966,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F11" s="7" t="s">
         <v>58</v>
       </c>
@@ -974,7 +974,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -985,7 +985,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -999,7 +999,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F14" s="7" t="s">
         <v>64</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>0.13</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F17" s="7" t="s">
         <v>70</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <f>A13*A16</f>
         <v>1.9500000000000002</v>
@@ -1063,7 +1063,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F20" s="7" t="s">
         <v>37</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F21" s="7" t="s">
         <v>77</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F22" s="7" t="s">
         <v>79</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F23" s="7" t="s">
         <v>81</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F24" s="7" t="s">
         <v>83</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F25" s="7" t="s">
         <v>85</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F26" s="7" t="s">
         <v>87</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F27" s="7" t="s">
         <v>89</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F28" s="7" t="s">
         <v>91</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F29" s="7" t="s">
         <v>93</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F30" s="7" t="s">
         <v>95</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F31" s="7" t="s">
         <v>97</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F32" s="7" t="s">
         <v>99</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F33" s="7" t="s">
         <v>101</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F34" s="7" t="s">
         <v>103</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F35" s="7" t="s">
         <v>105</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F36" s="7" t="s">
         <v>107</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F37" s="7" t="s">
         <v>109</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F38" s="7" t="s">
         <v>111</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F39" s="7" t="s">
         <v>113</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F40" s="7" t="s">
         <v>115</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F41" s="7" t="s">
         <v>117</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F42" s="7" t="s">
         <v>119</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F43" s="7" t="s">
         <v>121</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F44" s="7" t="s">
         <v>123</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F45" s="7" t="s">
         <v>125</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F46" s="7" t="s">
         <v>127</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F47" s="7" t="s">
         <v>129</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F48" s="7" t="s">
         <v>131</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="7" t="s">
         <v>133</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.75">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" s="7" t="s">
         <v>135</v>
       </c>
@@ -1322,32 +1322,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5219AD4A-B58F-488A-85D3-8AC59C46BE97}">
   <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -1363,12 +1363,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.40625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.9500000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>1.9500000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>

--- a/InputData/elec/BZECfNP/BAU Zero Emis Credit for Nuc Plants.xlsx
+++ b/InputData/elec/BZECfNP/BAU Zero Emis Credit for Nuc Plants.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\elec\BZECfNP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\elec\BZECfNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DB0CD19-45FE-44D4-B4CE-FAC067FEFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55FEC13C-BCC6-45EB-AD90-CE76B20A9252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="660" windowWidth="16755" windowHeight="14505" activeTab="1" xr2:uid="{C5EFE8E4-8660-49B5-88C2-8D099D44E411}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C5EFE8E4-8660-49B5-88C2-8D099D44E411}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="BZECfNP" sheetId="2" r:id="rId3"/>
+    <sheet name="BZECfNP" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
   <si>
     <t>BZECfNP BAU Zero Emissions Credit for Nuclear Plants</t>
   </si>
@@ -148,121 +147,139 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
+    <t>States with nuclear support</t>
+  </si>
+  <si>
+    <t>new york</t>
+  </si>
+  <si>
+    <t>illinois</t>
+  </si>
+  <si>
+    <t>new jersey</t>
+  </si>
+  <si>
+    <t>connecticut</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>KY</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
     <t>Maryland</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>AK</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>Connecticut</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>Delaware</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>Florida</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>Hawaii</t>
-  </si>
-  <si>
-    <t>HI</t>
-  </si>
-  <si>
-    <t>Idaho</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Illinois</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Indiana</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>KS</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t>KY</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>Maine</t>
-  </si>
-  <si>
-    <t>ME</t>
   </si>
   <si>
     <t>MD</t>
@@ -452,7 +469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,7 +503,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF333333"/>
+      <color rgb="FF403F41"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF403F41"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,7 +544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -531,6 +556,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -550,9 +578,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -590,7 +618,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -696,7 +724,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -838,7 +866,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -846,39 +874,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD24FED-1FE2-4888-B6B4-6A2AD33A9CF5}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C1" s="8">
-        <v>45293</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46185</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B2" t="str">
-        <f>LOOKUP(B1,F1:G50,G1:G50)</f>
+        <f>LOOKUP(B1,F2:G51,G2:G51)</f>
         <v>ND</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -886,106 +914,106 @@
         <v>3</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B4" s="4">
         <v>2019</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F7" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F11" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>15</v>
       </c>
@@ -993,322 +1021,346 @@
         <v>10</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F14" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
-        <v>0.13</v>
+        <f>IF(COUNTIF(A23:A26,B1),100%,0)</f>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F17" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6">
         <f>A13*A16</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F22" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
       <c r="F23" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
       <c r="F24" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
       <c r="F25" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
       <c r="F26" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F27" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F28" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F29" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F30" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F31" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="F32" s="7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F33" s="7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F34" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F35" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F36" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F37" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F38" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F39" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F40" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F41" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F42" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F43" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F44" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F45" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F46" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F47" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F48" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F49" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.45">
       <c r="F50" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.45">
+      <c r="F51" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1320,55 +1372,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5219AD4A-B58F-488A-85D3-8AC59C46BE97}">
-  <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E711EE28-FA43-4667-9C9B-C8367E936C88}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1477,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1558,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1653,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1748,132 +1762,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
         <f>About!$A$19</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f>$B5</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" ref="D5:AE5" si="0">$B5</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>1.9500000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1968,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2063,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2158,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2253,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2348,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2443,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2538,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2633,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2728,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2823,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2918,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3013,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -3108,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3203,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -3298,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3393,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3488,132 +3502,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23">
         <f>About!$A$19</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <f>$B23</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:AE23" si="1">$B23</f>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="U23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="W23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Y23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AC23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AD23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <f t="shared" si="1"/>
-        <v>1.9500000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -3708,7 +3722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>36</v>
       </c>
